--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/cirno.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/cirno.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD12ECFC-DA8B-422C-8E7A-28B15A1686AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744B1A77-91CC-401D-B71D-E19D699C3534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="23385" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="38">
   <si>
     <t>Attribute Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -31,6 +31,58 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Health</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MovementSpeed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HealthRecovery</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defense</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScanRangeMultiplier</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExpGainIncrease</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CooldownDecrease</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackStrength</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectileSpeedChange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectileSizeChange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectileDurationChange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectileIncreaseCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Lucky</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -108,55 +160,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>HpMax</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Speed</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRegen</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Armor</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PickRange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExpGain</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cooldown</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjSpeed</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjSize</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjLifetime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjCount</t>
+    <t>HealthRegeneration</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -480,7 +484,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24.625" customWidth="1"/>
@@ -498,7 +502,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -510,7 +514,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -522,7 +526,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -534,7 +538,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -542,7 +546,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -550,7 +554,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -558,7 +562,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -566,7 +570,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -574,7 +578,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -582,7 +586,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -594,7 +598,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -605,7 +609,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -617,7 +621,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -625,7 +629,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -633,7 +637,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>2</v>
@@ -641,7 +645,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -649,10 +653,18 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -673,19 +685,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -693,16 +705,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>0.05</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -710,16 +722,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>0.01</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -727,16 +739,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>0.01</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -744,16 +756,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>0.01</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -761,16 +773,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>0.01</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -778,16 +790,16 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C7">
         <v>0.01</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -795,16 +807,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C8">
         <v>0.01</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -812,16 +824,16 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C9">
         <v>0.01</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -829,16 +841,16 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C10">
         <v>0.01</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -846,16 +858,16 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C11">
         <v>0.01</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -863,16 +875,16 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C12">
         <v>0.01</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -880,16 +892,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C13">
         <v>0.01</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -897,16 +909,16 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C14">
         <v>0.01</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -914,16 +926,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>0.01</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -931,16 +943,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C16">
         <v>0.01</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -948,16 +960,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <v>0.01</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -965,16 +977,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C18">
         <v>0.01</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -982,16 +994,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C19">
         <v>0.01</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -999,16 +1011,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C20">
         <v>0.01</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1016,16 +1028,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C21">
         <v>0.01</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1033,16 +1045,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C22">
         <v>0.01</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1050,16 +1062,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C23">
         <v>0.01</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1067,16 +1079,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C24">
         <v>0.01</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1084,16 +1096,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C25">
         <v>0.01</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1101,16 +1113,16 @@
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C26">
         <v>0.01</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1118,16 +1130,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C27">
         <v>0.01</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1135,16 +1147,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C28">
         <v>0.01</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1152,16 +1164,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C29">
         <v>0.01</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1169,16 +1181,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C30">
         <v>1.01</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1186,16 +1198,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C31">
         <v>2.0099999999999998</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1203,16 +1215,16 @@
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C32">
         <v>3.01</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1220,16 +1232,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C33">
         <v>4.01</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1237,16 +1249,16 @@
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C34">
         <v>5.01</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1254,16 +1266,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C35">
         <v>6.01</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1271,16 +1283,16 @@
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C36">
         <v>7.01</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1288,16 +1300,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C37">
         <v>8.01</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1305,16 +1317,16 @@
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C38">
         <v>9.01</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1322,16 +1334,16 @@
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C39">
         <v>10.01</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1339,16 +1351,16 @@
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C40">
         <v>11.01</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/cirno.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/cirno.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D838D48-2194-4A40-B4BD-F93239C060D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744B1A77-91CC-401D-B71D-E19D699C3534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="38">
   <si>
     <t>Attribute Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -157,6 +157,10 @@
   </si>
   <si>
     <t>이동속도 0.05 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HealthRegeneration</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -480,7 +484,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24.625" customWidth="1"/>
@@ -653,6 +657,14 @@
       </c>
       <c r="B18">
         <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/cirno.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/cirno.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D838D48-2194-4A40-B4BD-F93239C060D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD12ECFC-DA8B-422C-8E7A-28B15A1686AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="23385" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="1" r:id="rId1"/>
@@ -31,58 +31,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Health</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MovementSpeed</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HealthRecovery</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Defense</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanRangeMultiplier</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExpGainIncrease</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CooldownDecrease</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackStrength</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileSpeedChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileSizeChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileDurationChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileIncreaseCount</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Lucky</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -157,6 +105,58 @@
   </si>
   <si>
     <t>이동속도 0.05 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpMax</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRegen</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PickRange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExpGain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cooldown</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjSpeed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjLifetime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjCount</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -498,7 +498,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -510,7 +510,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -534,7 +534,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -542,7 +542,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -550,7 +550,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -566,7 +566,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -574,7 +574,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -582,7 +582,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -605,7 +605,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -617,7 +617,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -625,7 +625,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -633,7 +633,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B16">
         <v>2</v>
@@ -641,7 +641,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -649,7 +649,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B18">
         <v>3</v>
@@ -673,19 +673,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -693,16 +693,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C2">
         <v>0.05</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -710,16 +710,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>0.01</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -727,16 +727,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>0.01</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -744,16 +744,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>0.01</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -761,16 +761,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>0.01</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -778,16 +778,16 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <v>0.01</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -795,16 +795,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C8">
         <v>0.01</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -812,16 +812,16 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C9">
         <v>0.01</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -829,16 +829,16 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>0.01</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -846,16 +846,16 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C11">
         <v>0.01</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -863,16 +863,16 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C12">
         <v>0.01</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -880,16 +880,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C13">
         <v>0.01</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -897,16 +897,16 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C14">
         <v>0.01</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -914,16 +914,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C15">
         <v>0.01</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -931,16 +931,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C16">
         <v>0.01</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -948,16 +948,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>0.01</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -965,16 +965,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C18">
         <v>0.01</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -982,16 +982,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C19">
         <v>0.01</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -999,16 +999,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C20">
         <v>0.01</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1016,16 +1016,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C21">
         <v>0.01</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1033,16 +1033,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C22">
         <v>0.01</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1050,16 +1050,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>0.01</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1067,16 +1067,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C24">
         <v>0.01</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1084,16 +1084,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C25">
         <v>0.01</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1101,16 +1101,16 @@
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C26">
         <v>0.01</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1118,16 +1118,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C27">
         <v>0.01</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1135,16 +1135,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C28">
         <v>0.01</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1152,16 +1152,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C29">
         <v>0.01</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1169,16 +1169,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C30">
         <v>1.01</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1186,16 +1186,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C31">
         <v>2.0099999999999998</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1203,16 +1203,16 @@
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C32">
         <v>3.01</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1220,16 +1220,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C33">
         <v>4.01</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1237,16 +1237,16 @@
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C34">
         <v>5.01</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1254,16 +1254,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C35">
         <v>6.01</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1271,16 +1271,16 @@
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C36">
         <v>7.01</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1288,16 +1288,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C37">
         <v>8.01</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1305,16 +1305,16 @@
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C38">
         <v>9.01</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1322,16 +1322,16 @@
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C39">
         <v>10.01</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1339,16 +1339,16 @@
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C40">
         <v>11.01</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/cirno.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/cirno.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744B1A77-91CC-401D-B71D-E19D699C3534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6642AB14-059C-49F5-8D46-7B83389A4D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="1" r:id="rId1"/>
@@ -31,58 +31,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Health</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MovementSpeed</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HealthRecovery</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Defense</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanRangeMultiplier</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExpGainIncrease</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CooldownDecrease</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackStrength</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileSpeedChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileSizeChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileDurationChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileIncreaseCount</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Lucky</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -160,7 +108,59 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>HealthRegeneration</t>
+    <t>HpMax</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRegen</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PickRange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExpGain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cooldown</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Knockback</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjSpeed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjLifetime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpellCardGaugeAcquisitionRateChange</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -487,7 +487,8 @@
   <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="24.625" customWidth="1"/>
+    <col min="1" max="1" width="48.625" customWidth="1"/>
+    <col min="2" max="2" width="24.625" customWidth="1"/>
     <col min="3" max="11" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -502,7 +503,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -514,22 +515,18 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+        <v>0.01</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4">
         <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -538,15 +535,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B5">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -554,7 +555,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -562,7 +563,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -570,15 +571,15 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -586,42 +587,31 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -629,7 +619,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -637,34 +627,34 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="B19">
-        <v>0.01</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -685,19 +675,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -705,16 +695,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C2">
         <v>0.05</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -722,16 +712,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>0.01</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -739,16 +729,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>0.01</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -756,16 +746,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>0.01</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -773,16 +763,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C6">
         <v>0.01</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -790,16 +780,16 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>0.01</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -807,16 +797,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C8">
         <v>0.01</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -824,16 +814,16 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C9">
         <v>0.01</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -841,16 +831,16 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C10">
         <v>0.01</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -858,16 +848,16 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>0.01</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -875,16 +865,16 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C12">
         <v>0.01</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -892,16 +882,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C13">
         <v>0.01</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -909,16 +899,16 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C14">
         <v>0.01</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -926,16 +916,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C15">
         <v>0.01</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -943,16 +933,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C16">
         <v>0.01</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -960,16 +950,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C17">
         <v>0.01</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -977,16 +967,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>0.01</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -994,16 +984,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C19">
         <v>0.01</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1011,16 +1001,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C20">
         <v>0.01</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1028,16 +1018,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C21">
         <v>0.01</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1045,16 +1035,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C22">
         <v>0.01</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1062,16 +1052,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C23">
         <v>0.01</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1079,16 +1069,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>0.01</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1096,16 +1086,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C25">
         <v>0.01</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1113,16 +1103,16 @@
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C26">
         <v>0.01</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1130,16 +1120,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C27">
         <v>0.01</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1147,16 +1137,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C28">
         <v>0.01</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1164,16 +1154,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C29">
         <v>0.01</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1181,16 +1171,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C30">
         <v>1.01</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1198,16 +1188,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C31">
         <v>2.0099999999999998</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1215,16 +1205,16 @@
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C32">
         <v>3.01</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1232,16 +1222,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C33">
         <v>4.01</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1249,16 +1239,16 @@
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C34">
         <v>5.01</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1266,16 +1256,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C35">
         <v>6.01</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1283,16 +1273,16 @@
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C36">
         <v>7.01</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1300,16 +1290,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C37">
         <v>8.01</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1317,16 +1307,16 @@
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C38">
         <v>9.01</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1334,16 +1324,16 @@
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C39">
         <v>10.01</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1351,16 +1341,16 @@
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C40">
         <v>11.01</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/cirno.xlsx
+++ b/TouhouSurvival/Assets/StreamingAssets/AttributeTables/PlayableCharacters/cirno.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\TouhouSurvival\TouhouSurvival\Assets\StreamingAssets\AttributeTables\PlayableCharacters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744B1A77-91CC-401D-B71D-E19D699C3534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9630F1CF-5870-4CBA-9402-BD69175BF0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="23385" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="37">
   <si>
     <t>Attribute Type</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -31,58 +31,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Health</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MovementSpeed</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HealthRecovery</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Defense</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScanRangeMultiplier</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExpGainIncrease</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CooldownDecrease</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackStrength</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileSpeedChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileSizeChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileDurationChange</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ProjectileIncreaseCount</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Lucky</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -160,7 +108,55 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>HealthRegeneration</t>
+    <t>HpMax</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRegen</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PickRange</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExpGain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cooldown</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjSpeed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjLifetime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjCount</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -484,7 +480,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24.625" customWidth="1"/>
@@ -502,7 +498,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -514,7 +510,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -526,7 +522,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -538,15 +534,15 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -554,15 +550,15 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -570,7 +566,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -578,50 +574,50 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -629,41 +625,33 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19">
         <v>0.01</v>
       </c>
     </row>
@@ -685,19 +673,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -705,16 +693,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C2">
         <v>0.05</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -722,16 +710,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>0.01</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -739,16 +727,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>0.01</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -756,16 +744,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>0.01</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -773,16 +761,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>0.01</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -790,16 +778,16 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <v>0.01</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -807,16 +795,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C8">
         <v>0.01</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -824,16 +812,16 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C9">
         <v>0.01</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -841,16 +829,16 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>0.01</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -858,16 +846,16 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C11">
         <v>0.01</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -875,16 +863,16 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C12">
         <v>0.01</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -892,16 +880,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C13">
         <v>0.01</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -909,16 +897,16 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C14">
         <v>0.01</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -926,16 +914,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C15">
         <v>0.01</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -943,16 +931,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C16">
         <v>0.01</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -960,16 +948,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>0.01</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -977,16 +965,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C18">
         <v>0.01</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -994,16 +982,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C19">
         <v>0.01</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1011,16 +999,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C20">
         <v>0.01</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1028,16 +1016,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C21">
         <v>0.01</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1045,16 +1033,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C22">
         <v>0.01</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1062,16 +1050,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>0.01</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1079,16 +1067,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C24">
         <v>0.01</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1096,16 +1084,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C25">
         <v>0.01</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1113,16 +1101,16 @@
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C26">
         <v>0.01</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1130,16 +1118,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C27">
         <v>0.01</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1147,16 +1135,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C28">
         <v>0.01</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1164,16 +1152,16 @@
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C29">
         <v>0.01</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1181,16 +1169,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C30">
         <v>1.01</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1198,16 +1186,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C31">
         <v>2.0099999999999998</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1215,16 +1203,16 @@
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C32">
         <v>3.01</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1232,16 +1220,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C33">
         <v>4.01</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1249,16 +1237,16 @@
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C34">
         <v>5.01</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1266,16 +1254,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C35">
         <v>6.01</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1283,16 +1271,16 @@
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C36">
         <v>7.01</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1300,16 +1288,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C37">
         <v>8.01</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1317,16 +1305,16 @@
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C38">
         <v>9.01</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1334,16 +1322,16 @@
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C39">
         <v>10.01</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1351,16 +1339,16 @@
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C40">
         <v>11.01</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
